--- a/results/operaciones_20240131.xlsx
+++ b/results/operaciones_20240131.xlsx
@@ -446,77 +446,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>IUSN.DE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>3165</v>
       </c>
       <c r="C2" t="n">
-        <v>188.4499969482422</v>
+        <v>6.317999839782715</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00142889554167749</v>
+        <v>0.0401379676723224</v>
       </c>
       <c r="E2" t="n">
-        <v>188.7192723087107</v>
+        <v>6.571591513105651</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>923</v>
+        <v>205</v>
       </c>
       <c r="C3" t="n">
-        <v>20.90999984741211</v>
+        <v>97.43787384033203</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01203366869683108</v>
+        <v>0.002711328057339119</v>
       </c>
       <c r="E3" t="n">
-        <v>21.16162385802665</v>
+        <v>97.7020598815228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DBA</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1056</v>
+        <v>534</v>
       </c>
       <c r="C4" t="n">
-        <v>20.0571231842041</v>
+        <v>37.44427108764648</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01299104900690917</v>
+        <v>0.006923460957989279</v>
       </c>
       <c r="E4" t="n">
-        <v>20.31768625442771</v>
+        <v>37.70351503662217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240</v>
+        <v>147</v>
       </c>
       <c r="C5" t="n">
-        <v>88.25801849365234</v>
+        <v>135.2410888671875</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002964305734749769</v>
+        <v>0.001957115739249216</v>
       </c>
       <c r="E5" t="n">
-        <v>88.51964224401073</v>
+        <v>135.5057713308027</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +526,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>89.09431457519531</v>
+        <v>89.09429168701172</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002934810375180607</v>
+        <v>0.002934810480118489</v>
       </c>
       <c r="E6" t="n">
-        <v>89.3557894939802</v>
+        <v>89.3557665479735</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.870756120459384</v>
+        <v>1.399394455132613</v>
       </c>
       <c r="C7" t="n">
         <v>140.0350036621094</v>
